--- a/TESTS/zlit_5_pani_metelytsia.xlsx
+++ b/TESTS/zlit_5_pani_metelytsia.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Брати Якоб і Вільгельм Грімм — знамениті збирачі і обробники народних казок</t>
+          <t>Брати Якоб і Вільгельм Грімм</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>До збірника казок братів Грімм — вони зібрали і записали десятки народних казок Німеччини</t>
+          <t>До збірника казок братів Грімм</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Німецькій — брати Грімм збирали фольклор німецького народу</t>
+          <t>Німецькій</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Щоб позбутися її — веретено впало в криницю і вона змусила дівчину стрибнути за ним</t>
+          <t>Щоб позбутися її</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -813,6 +843,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Казка пояснює сніг як пір'я що вилітає з перини Пані Метелиці — народне пояснення природного явища</t>
+          <t>Казка пояснює сніг як пір'я що вилітає з перини Пані Метелиці</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Старанно виконувала всю роботу — поливала квіти мела двір і не скаржилась</t>
+          <t>Старанно виконувала всю роботу</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чому падчерка щодня сиділа біля криниці й пряла, аж поки не вколола палець?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Це була її розвага</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мачуха суворо наказала їй прясти біля криниці, доки не закривавить палець нитку</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона сама хотіла там сидіти</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона ховалась там від мачухи</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що сталося з веретеном, коли падчерка нахилилася над криницею, щоб обмити кров?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Воно зламалось</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Веретено випало з рук і впало на дно криниці</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона його загубила сама</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Мачуха забрала його</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Як мачуха відреагувала, коли дізналась про загублене веретено?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заспокоїла дівчину</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розгнівано наказала падчерці стрибнути в криницю й дістати веретено будь-що</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сама пішла за веретеном</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сказала забути про нього</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Кого/що першим зустріла дівчина, опинившись у дивовижному краї під криницею?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Річку</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Піч, повну хліба, що просив його вийняти, бо вже спікся</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Замок</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ліс</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що дівчина зробила, побачивши яблуню, обтяжену стиглими яблуками, яка просила про допомогу?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пройшла мимо</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обтрусила всі яблука з дерева, як воно й просило</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зірвала лише одне яблуко</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не звернула уваги</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чому дівчина допомагала печі й яблуні, хоча й поспішала до Пані Метелиці?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Боялась покарання</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона була доброю і чуйною за вдачею, готовою допомогти кожному</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Це було по дорозі, неважко</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їй наказали духи</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Якою на вигляд була Пані Метелиця, коли дівчина вперше її побачила?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Молодою красунею</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Старою жінкою з такими великими зубами, що дівчина спершу злякалась</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Невидимою істотою</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дитиною</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що Пані Метелиця запропонувала дівчині, побачивши, що та не злякалась і залишилась?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу відіслала додому</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Запропонувала служити в неї, пообіцявши добре віддячити за гарну роботу</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покарала її</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не запропонувала</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Скільки часу дівчина прослужила у Пані Метелиці, перш ніж почала тужити за домом?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Один день</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Якийсь час — достатньо, щоб втомитися й затужити, хоч жилося їй непогано</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Багато років</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише годину</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Чому дівчина зрештою попросила Пані Метелицю відпустити її додому?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Її прогнали</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона затужила за рідним домом, навіть попри сувору мачуху</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Робота стала занадто важкою</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пані Метелиця їй надокучила</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Пані Метелиця поставилась до бажання дівчини повернутися додому?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розгнівалась і не відпустила</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З розумінням відпустила її, похваливши за старанну службу</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Заплакала</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Запропонувала залишитись назавжди силою</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що Пані Метелиця зробила, коли провела дівчину до великих воріт перед поверненням додому?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого особливого</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Коли дівчина проходила крізь ворота, на неї пролився справжній золотий дощ, що прилип до неї</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дала їй грошей у мішку</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подарувала сукню</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Як зустріли вдома дівчину, обсипану золотом?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніхто не помітив</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мачуха та її донька зраділи золоту і вирішили, що ледача донька теж має спробувати щастя</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дівчину прогнали</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Її покарали за запізнення</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як поводилась рідна донька мачухи, коли сама пішла до криниці за веретеном?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Старанно, як і падчерка</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кинула веретено в криницю навмисно, щоб теж потрапити в чарівний край</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Відмовилась іти взагалі</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заблукала по дорозі</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як лінива донька повелася з піччю та яблунею на шляху до Пані Метелиці?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Допомогла, як і падчерка</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пройшла мимо, не захотівши бруднити руки чи витрачати час</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Допомогла лише печі</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Допомогла лише яблуні</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Як лінива донька служила у Пані Метелиці перші дні?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Старанно і охайно</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спершу намагалась працювати, але швидко почала лінуватися й нарікати</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Відмовилась працювати одразу</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Працювала краще за падчерку</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому лінива донька захотіла піти від Пані Метелиці так швидко?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Затужила за домом, як і падчерка</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Їй просто стало нудно й важко працювати, і вона вирішила, що вже заслужила нагороду</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пані Метелиця її прогнала</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Робота скінчилась</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що сталося, коли лінива донька проходила крізь ті самі ворота наприкінці служби?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На неї теж пролився золотий дощ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Замість золота на неї вилився великий казан смоли</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нічого не сталось</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ворота не відчинились</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Чому саме смола, а не золото, стала «нагородою» для ледачої доньки?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Це сталось випадково</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Нагорода в казці відповідає не намірам, а реальним вчинкам і праці людини</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пані Метелиця помилилась</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заздрість падчерки наклала прокляття</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чи змилась смола з ледачої доньки, коли вона повернулась додому?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так, одразу</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ні — смола так і залишилась на ній до кінця її днів</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Змилась за тиждень</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Невідомо</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яке протиставлення лежить в основі всієї казки «Пані Метелиця»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Багатство і бідність</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Праця, доброта і скромність проти лінощів, грубості й жадібності</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Краса і потворність зовнішня</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сміливість і страх</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Який природний феномен казково пояснює «Пані Метелиця»?</t>
+          <t>Казка «Пані Метелиця» казково пояснює, чому йде сніг — це пір'я з перини, яку вона трусить.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Які типові риси народної казки є у «Пані Метелиці»?</t>
+          <t>У казці «Пані Метелиця» є типові для народних казок повтори дій і протиставлення двох героїнь.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє мачуха у казці?</t>
+          <t>Мачуха в казці зображена доброю і справедливою до обох дівчат однаково.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Який символічний сенс має «золотий дощ» і «смоляний дощ» у казці?</t>
+          <t>«Золотий дощ» символізує нагороду за працьовитість і доброту, а «смоляний дощ» — покарання за лінощі.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея казки «Пані Метелиця»?</t>
+          <t>Образ Пані Метелиці символізує сувору, але справедливу силу, що винагороджує за чесноти.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що означає образ Пані Метелиці у казці?</t>
+          <t>Головна ідея казки — заможні люди завжди отримують краще, ніж бідні, незалежно від вчинків.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси характеру падчерки розкриває казка?</t>
+          <t>Що сталося з падчеркою на її шляху до Пані Метелиці та назад?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Працьовитість</t>
+          <t>Випустила веретено в криницю</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Лінощі</t>
+          <t>Допомогла печі й яблуні</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Сумлінність</t>
+          <t>Отримала смолу замість золота</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Доброта і терплячість</t>
+          <t>Чесно прослужила і повернулась додому</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,В,Г</t>
+          <t>А,Б,Г</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Золотий дощ — коли вона проходила під воротами на неї злинуло золото яке залишилось при ній</t>
+          <t>Золотий дощ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Бо вона була лінивою і нечесною — вдавала що працює а насправді лише чекала винагороди</t>
+          <t>Бо вона була лінивою і нечесною</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
